--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.49443696431362</v>
+        <v>3.492846006700964</v>
       </c>
       <c r="D2" t="n">
-        <v>22.05962910056022</v>
+        <v>3.584689728841036</v>
       </c>
       <c r="E2" t="n">
-        <v>8.867082837321195</v>
+        <v>1.440900961064694</v>
       </c>
       <c r="F2" t="n">
-        <v>8.192107716867163</v>
+        <v>1.331217503990914</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.35386974601592</v>
+        <v>4.445003833727586</v>
       </c>
       <c r="D3" t="n">
-        <v>27.63562544449713</v>
+        <v>4.490789134730784</v>
       </c>
       <c r="E3" t="n">
-        <v>8.867082837321195</v>
+        <v>1.440900961064694</v>
       </c>
       <c r="F3" t="n">
-        <v>8.192107716867163</v>
+        <v>1.331217503990914</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.05531846734699</v>
+        <v>2.608989250943886</v>
       </c>
       <c r="D4" t="n">
-        <v>15.57657278018818</v>
+        <v>2.531193076780579</v>
       </c>
       <c r="E4" t="n">
-        <v>8.867082837321195</v>
+        <v>1.440900961064694</v>
       </c>
       <c r="F4" t="n">
-        <v>8.192107716867163</v>
+        <v>1.331217503990914</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.35201466131355</v>
+        <v>5.419702382463453</v>
       </c>
       <c r="D5" t="n">
-        <v>31.71159094085316</v>
+        <v>5.153133527888638</v>
       </c>
       <c r="E5" t="n">
-        <v>8.867082837321195</v>
+        <v>1.440900961064694</v>
       </c>
       <c r="F5" t="n">
-        <v>8.192107716867163</v>
+        <v>1.331217503990914</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.653100383548377</v>
+        <v>1.081128812326611</v>
       </c>
       <c r="D6" t="n">
-        <v>8.284020762890446</v>
+        <v>1.346153373969698</v>
       </c>
       <c r="E6" t="n">
-        <v>8.867082837321195</v>
+        <v>1.440900961064694</v>
       </c>
       <c r="F6" t="n">
-        <v>8.192107716867163</v>
+        <v>1.331217503990914</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.59338242994734</v>
+        <v>4.646424644866443</v>
       </c>
       <c r="D7" t="n">
-        <v>28.92819676602711</v>
+        <v>4.700831974479406</v>
       </c>
       <c r="E7" t="n">
-        <v>8.867082837321195</v>
+        <v>1.440900961064694</v>
       </c>
       <c r="F7" t="n">
-        <v>8.192107716867163</v>
+        <v>1.331217503990914</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
